--- a/08-Corrective-Actions/Corrective-Action-Plan.xlsx
+++ b/08-Corrective-Actions/Corrective-Action-Plan.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
   <si>
-    <t xml:space="preserve">Simulated portfolio project - SecurePay Technologies Pvt. Ltd. is fictional. Not a certification claim.</t>
+    <t xml:space="preserve">Simulated portfolio project - HawkPay Technologies Pvt. Ltd. is fictional. Not a certification claim.</t>
   </si>
   <si>
     <t xml:space="preserve">Finding</t>
